--- a/vse-loti/341139911/spec-341139911.xlsx
+++ b/vse-loti/341139911/spec-341139911.xlsx
@@ -84,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +97,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -465,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -558,7 +561,7 @@
         <v>149783.72</v>
       </c>
       <c r="I2" s="5" t="n">
-        <v>179740.46</v>
+        <v>182736.14</v>
       </c>
     </row>
     <row r="3">
@@ -593,7 +596,7 @@
         <v>739949.52</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>887939.42</v>
+        <v>902738.41</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +631,7 @@
         <v>163409.6</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>196091.52</v>
+        <v>199359.71</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +666,7 @@
         <v>126044.4</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>151253.29</v>
+        <v>153774.17</v>
       </c>
     </row>
     <row r="6">
@@ -698,7 +701,7 @@
         <v>210670.57</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>252804.68</v>
+        <v>257018.09</v>
       </c>
     </row>
     <row r="7">
@@ -733,7 +736,7 @@
         <v>153042.25</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>183650.7</v>
+        <v>186711.54</v>
       </c>
     </row>
     <row r="8">
@@ -768,7 +771,7 @@
         <v>148695.42</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>178434.51</v>
+        <v>181408.42</v>
       </c>
     </row>
     <row r="9">
@@ -803,7 +806,7 @@
         <v>146686.5</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>176023.8</v>
+        <v>178957.53</v>
       </c>
     </row>
     <row r="10">
@@ -838,7 +841,7 @@
         <v>495617.98</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>594741.58</v>
+        <v>604653.9399999999</v>
       </c>
     </row>
     <row r="11">
@@ -873,7 +876,7 @@
         <v>188408.05</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>226089.66</v>
+        <v>229857.82</v>
       </c>
     </row>
     <row r="12">
@@ -908,7 +911,7 @@
         <v>1027667.63</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>1233201.15</v>
+        <v>1253754.51</v>
       </c>
     </row>
     <row r="13">
@@ -943,7 +946,7 @@
         <v>251344.02</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>301612.83</v>
+        <v>306639.71</v>
       </c>
     </row>
     <row r="14">
@@ -969,18 +972,35 @@
         <v>1728674.432527768</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>НМЦК с НДС 22% (справочно):</t>
+        </is>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>2108982.81</v>
+      </c>
+    </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
+          <t>Ставка НДС в документах не указана, расчёт справочный по 22 %; суммы источника указаны без НДС: "без НДС" — Kommercheskoe predlozhenie (Struktura NMTs).txt. «без НДС» — сумма из документа, «с НДС» = сумма × 1,22.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
           <t>Источник: Коммерческое предложение (Структура НМЦ).xlsx</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A17:B19"/>
+    <mergeCell ref="A19:B21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/vse-loti/341139911/spec-341139911.xlsx
+++ b/vse-loti/341139911/spec-341139911.xlsx
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -480,6 +480,7 @@
     <col width="20.28515625" customWidth="1" min="7" max="7"/>
     <col width="18.85546875" customWidth="1" min="8" max="8"/>
     <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="18.85546875" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -515,17 +516,22 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Цена за т (без НДС)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Стоимость (без НДС)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Цена за т (без НДС)</t>
-        </is>
-      </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Цена за т (с НДС)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Стоимость (с НДС)</t>
         </is>
       </c>
     </row>
@@ -555,13 +561,16 @@
         <v>1.283</v>
       </c>
       <c r="G2" s="5" t="n">
+        <v>149783.72</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>192155.74</v>
-      </c>
-      <c r="H2" s="5" t="n">
-        <v>149783.72</v>
       </c>
       <c r="I2" s="5" t="n">
         <v>182736.14</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>234430</v>
       </c>
     </row>
     <row r="3">
@@ -590,13 +599,16 @@
         <v>0.083</v>
       </c>
       <c r="G3" s="5" t="n">
+        <v>739949.52</v>
+      </c>
+      <c r="H3" s="5" t="n">
         <v>61608.2</v>
-      </c>
-      <c r="H3" s="5" t="n">
-        <v>739949.52</v>
       </c>
       <c r="I3" s="5" t="n">
         <v>902738.41</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>75162</v>
       </c>
     </row>
     <row r="4">
@@ -625,13 +637,16 @@
         <v>7.38</v>
       </c>
       <c r="G4" s="5" t="n">
+        <v>163409.6</v>
+      </c>
+      <c r="H4" s="5" t="n">
         <v>1205954.92</v>
-      </c>
-      <c r="H4" s="5" t="n">
-        <v>163409.6</v>
       </c>
       <c r="I4" s="5" t="n">
         <v>199359.71</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>1471265</v>
       </c>
     </row>
     <row r="5">
@@ -660,13 +675,16 @@
         <v>0.321</v>
       </c>
       <c r="G5" s="5" t="n">
+        <v>126044.4</v>
+      </c>
+      <c r="H5" s="5" t="n">
         <v>40409.84</v>
-      </c>
-      <c r="H5" s="5" t="n">
-        <v>126044.4</v>
       </c>
       <c r="I5" s="5" t="n">
         <v>153774.17</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>49300</v>
       </c>
     </row>
     <row r="6">
@@ -695,13 +713,16 @@
         <v>0.094</v>
       </c>
       <c r="G6" s="5" t="n">
+        <v>210670.57</v>
+      </c>
+      <c r="H6" s="5" t="n">
         <v>19721.97</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>210670.57</v>
       </c>
       <c r="I6" s="5" t="n">
         <v>257018.09</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>24060.8</v>
       </c>
     </row>
     <row r="7">
@@ -730,13 +751,16 @@
         <v>0.075</v>
       </c>
       <c r="G7" s="5" t="n">
+        <v>153042.25</v>
+      </c>
+      <c r="H7" s="5" t="n">
         <v>11549.18</v>
-      </c>
-      <c r="H7" s="5" t="n">
-        <v>153042.25</v>
       </c>
       <c r="I7" s="5" t="n">
         <v>186711.54</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>14090</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +789,16 @@
         <v>0.142</v>
       </c>
       <c r="G8" s="5" t="n">
+        <v>148695.42</v>
+      </c>
+      <c r="H8" s="5" t="n">
         <v>21114.75</v>
-      </c>
-      <c r="H8" s="5" t="n">
-        <v>148695.42</v>
       </c>
       <c r="I8" s="5" t="n">
         <v>181408.42</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>25759.99</v>
       </c>
     </row>
     <row r="9">
@@ -800,13 +827,16 @@
         <v>0.518</v>
       </c>
       <c r="G9" s="5" t="n">
+        <v>146686.5</v>
+      </c>
+      <c r="H9" s="5" t="n">
         <v>75983.61</v>
-      </c>
-      <c r="H9" s="5" t="n">
-        <v>146686.5</v>
       </c>
       <c r="I9" s="5" t="n">
         <v>178957.53</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>92700</v>
       </c>
     </row>
     <row r="10">
@@ -835,13 +865,16 @@
         <v>0.025</v>
       </c>
       <c r="G10" s="5" t="n">
+        <v>495617.98</v>
+      </c>
+      <c r="H10" s="5" t="n">
         <v>12459.84</v>
-      </c>
-      <c r="H10" s="5" t="n">
-        <v>495617.98</v>
       </c>
       <c r="I10" s="5" t="n">
         <v>604653.9399999999</v>
+      </c>
+      <c r="J10" s="5" t="n">
+        <v>15201</v>
       </c>
     </row>
     <row r="11">
@@ -870,13 +903,16 @@
         <v>0.304</v>
       </c>
       <c r="G11" s="5" t="n">
+        <v>188408.05</v>
+      </c>
+      <c r="H11" s="5" t="n">
         <v>57245.9</v>
-      </c>
-      <c r="H11" s="5" t="n">
-        <v>188408.05</v>
       </c>
       <c r="I11" s="5" t="n">
         <v>229857.82</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>69840</v>
       </c>
     </row>
     <row r="12">
@@ -905,13 +941,16 @@
         <v>0.008</v>
       </c>
       <c r="G12" s="5" t="n">
+        <v>1027667.63</v>
+      </c>
+      <c r="H12" s="5" t="n">
         <v>8211.48</v>
-      </c>
-      <c r="H12" s="5" t="n">
-        <v>1027667.63</v>
       </c>
       <c r="I12" s="5" t="n">
         <v>1253754.51</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>10018.01</v>
       </c>
     </row>
     <row r="13">
@@ -940,14 +979,17 @@
         <v>0.089</v>
       </c>
       <c r="G13" s="5" t="n">
+        <v>251344.02</v>
+      </c>
+      <c r="H13" s="5" t="n">
         <v>22259.03</v>
-      </c>
-      <c r="H13" s="5" t="n">
-        <v>251344.02</v>
       </c>
       <c r="I13" s="5" t="n">
         <v>306639.71</v>
       </c>
+      <c r="J13" s="5" t="n">
+        <v>27156.02</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -959,7 +1001,16 @@
         <v>10.322</v>
       </c>
       <c r="G14" s="9" t="n">
+        <v>167474.76</v>
+      </c>
+      <c r="H14" s="9" t="n">
         <v>1728674.46</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>204319.21</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>2108982.84</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +1019,7 @@
           <t>НМЦК из обоснования:</t>
         </is>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="H15" s="9" t="n">
         <v>1728674.432527768</v>
       </c>
     </row>
@@ -978,7 +1029,7 @@
           <t>НМЦК с НДС 22% (справочно):</t>
         </is>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="J16" s="9" t="n">
         <v>2108982.81</v>
       </c>
     </row>
